--- a/frontend/public/templates/arbeitszeit-vorlage.xlsx
+++ b/frontend/public/templates/arbeitszeit-vorlage.xlsx
@@ -639,11 +639,7 @@
     <cellStyle name="Normalny" xfId="0" builtinId="0"/>
     <cellStyle name="Standard 2" xfId="1" xr:uid="{84FF2406-31F1-42CD-9A13-04086DCD9D07}"/>
   </cellStyles>
-  <dxfs count="1">
-    <dxf>
-      <numFmt numFmtId="202" formatCode="ddd\,\ dd;;"/>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1895,11 +1891,6 @@
     <mergeCell ref="H35:I35"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="B11:B42">
-    <cfRule type="expression" dxfId="0" priority="1" stopIfTrue="1">
-      <formula>ISNUMBER($H$7)</formula>
-    </cfRule>
-  </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.11811023622047245" right="0.11811023622047245" top="0.31496062992125984" bottom="0.11811023622047245" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="90" orientation="portrait" r:id="rId1"/>
